--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.197934876152641</v>
+        <v>0.1979348761526409</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727415</v>
+        <v>0.2056428338727416</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793944992</v>
+        <v>0.00315419079394504</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105778</v>
+        <v>0.01557029016105796</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191622</v>
+        <v>0.005855458830191725</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600637</v>
+        <v>0.00118618433860068</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333005</v>
+        <v>0.004753484704333037</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704332992</v>
+        <v>0.004753484704333024</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836723</v>
+        <v>0.002771926326836817</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402842</v>
+        <v>0.4792480623402844</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602263</v>
+        <v>0.02413727288602276</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451343</v>
+        <v>0.2745492459451341</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999154</v>
+        <v>0.01091136045999164</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1248,7 +1248,7 @@
         <v>37</v>
       </c>
       <c r="P16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q16">
         <v>15</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089466</v>
+        <v>0.5186239472089462</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462029</v>
+        <v>0.04986997364462024</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594959</v>
+        <v>0.0444812322159496</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578799</v>
+        <v>0.05378569674578823</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235184</v>
+        <v>0.1019516679235185</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999573</v>
+        <v>0.02689303999999582</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836721</v>
+        <v>0.002771926326836808</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793944993</v>
+        <v>0.003154190793945058</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620819</v>
+        <v>0.01468630870620832</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502744</v>
+        <v>0.01130002982502748</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502746</v>
+        <v>0.01130002982502748</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462026</v>
+        <v>0.04986997364462029</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652394</v>
+        <v>0.2852074932652391</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531604</v>
+        <v>0.1556265945531602</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097577</v>
+        <v>0.1963072587097575</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117341</v>
+        <v>0.6068633760117337</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072254</v>
+        <v>0.5270445030072248</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091476</v>
+        <v>0.05545829422091496</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588666</v>
+        <v>0.001236945685588667</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106584</v>
+        <v>0.06812048270106612</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301344</v>
+        <v>0.01089577315301349</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328445</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2556,7 +2556,7 @@
         <v>24</v>
       </c>
       <c r="P40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>14</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328446</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602264</v>
+        <v>0.02413727288602274</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565408997</v>
+        <v>0.04165861565409005</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579479</v>
+        <v>0.01871153087579481</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194804</v>
+        <v>0.003790535553194883</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127862</v>
+        <v>0.227998432712786</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603733</v>
+        <v>0.005298875417603748</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603752</v>
+        <v>0.005298875417603785</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685299</v>
+        <v>0.006905590848685278</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290831</v>
+        <v>0.03408863327290827</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449338</v>
+        <v>0.00214686610044937</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726889</v>
+        <v>0.08230408821726888</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409757</v>
+        <v>0.0002505773915409784</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850057</v>
+        <v>0.005447925395850115</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738926</v>
+        <v>0.5730798804738921</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542331</v>
+        <v>0.161368919454233</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652421</v>
+        <v>0.1969762873652422</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462029</v>
+        <v>0.04986997364462027</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359533</v>
+        <v>0.02452746104359534</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856284</v>
+        <v>0.3552799123856281</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422744</v>
+        <v>0.7252640270422732</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340304</v>
+        <v>0.1627043167340306</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727416</v>
+        <v>0.2056428338727419</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.00315419079394504</v>
+        <v>0.003154190793945111</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105796</v>
+        <v>0.01557029016105814</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191725</v>
+        <v>0.005855458830191881</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.00118618433860068</v>
+        <v>0.001186184338600706</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333037</v>
+        <v>0.004753484704333127</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704333024</v>
+        <v>0.004753484704333142</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836817</v>
+        <v>0.002771926326836873</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602276</v>
+        <v>0.02413727288602291</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999164</v>
+        <v>0.01091136045999191</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1248,7 +1248,7 @@
         <v>37</v>
       </c>
       <c r="P16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q16">
         <v>15</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089462</v>
+        <v>0.5186239472089463</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462024</v>
+        <v>0.04986997364462026</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.0444812322159496</v>
+        <v>0.04448123221594959</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578823</v>
+        <v>0.05378569674578838</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235185</v>
+        <v>0.1019516679235186</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999582</v>
+        <v>0.026893039999996</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836808</v>
+        <v>0.002771926326836873</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945058</v>
+        <v>0.003154190793945121</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620832</v>
+        <v>0.01468630870620847</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502748</v>
+        <v>0.01130002982502744</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502748</v>
+        <v>0.01130002982502744</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652391</v>
+        <v>0.2852074932652393</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531602</v>
+        <v>0.1556265945531603</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117337</v>
+        <v>0.6068633760117339</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072248</v>
+        <v>0.5270445030072247</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091496</v>
+        <v>0.05545829422091508</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588667</v>
+        <v>0.001236945685588712</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106612</v>
+        <v>0.06812048270106635</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301349</v>
+        <v>0.01089577315301354</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328442</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602274</v>
+        <v>0.02413727288602291</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409005</v>
+        <v>0.04165861565409014</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579481</v>
+        <v>0.01871153087579484</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194883</v>
+        <v>0.003790535553194929</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.227998432712786</v>
+        <v>0.2279984327127862</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603748</v>
+        <v>0.005298875417603865</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603785</v>
+        <v>0.005298875417603884</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685278</v>
+        <v>0.006905590848685266</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290827</v>
+        <v>0.03408863327290822</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.00214686610044937</v>
+        <v>0.002146866100449387</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726888</v>
+        <v>0.08230408821726889</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409784</v>
+        <v>0.0002505773915409655</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230429</v>
+        <v>0.121076913323043</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850115</v>
+        <v>0.005447925395850176</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738921</v>
+        <v>0.5730798804738931</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652422</v>
+        <v>0.1969762873652421</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462027</v>
+        <v>0.04986997364462029</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462026</v>
+        <v>0.04986997364462031</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359534</v>
+        <v>0.02452746104359536</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856281</v>
+        <v>0.3552799123856283</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422732</v>
+        <v>0.7252640270422737</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340306</v>
+        <v>0.1627043167340304</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -490,7 +490,7 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q2">
         <v>15</v>
@@ -545,7 +545,7 @@
         <v>19</v>
       </c>
       <c r="P3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q3">
         <v>11</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727419</v>
+        <v>0.2056428338727425</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793945111</v>
+        <v>0.003154190793945209</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105814</v>
+        <v>0.01557029016105854</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191881</v>
+        <v>0.005855458830192094</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600706</v>
+        <v>0.001186184338600782</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333127</v>
+        <v>0.004753484704333339</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704333142</v>
+        <v>0.004753484704333344</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836873</v>
+        <v>0.002771926326837039</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602291</v>
+        <v>0.02413727288602328</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="P14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q14">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999191</v>
+        <v>0.01091136045999227</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1248,7 +1248,7 @@
         <v>37</v>
       </c>
       <c r="P16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q16">
         <v>15</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089463</v>
+        <v>0.5186239472089467</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462026</v>
+        <v>0.04986997364462037</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594959</v>
+        <v>0.04448123221594966</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578838</v>
+        <v>0.05378569674578892</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235186</v>
+        <v>0.1019516679235187</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.026893039999996</v>
+        <v>0.02689303999999649</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836873</v>
+        <v>0.002771926326837044</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945121</v>
+        <v>0.003154190793945222</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620847</v>
+        <v>0.01468630870620876</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502744</v>
+        <v>0.01130002982502751</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502744</v>
+        <v>0.01130002982502749</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462029</v>
+        <v>0.04986997364462036</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652393</v>
+        <v>0.2852074932652396</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2012,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="P30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>11</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531603</v>
+        <v>0.1556265945531602</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2067,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="P31">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q31">
         <v>15</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097575</v>
+        <v>0.1963072587097576</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2122,7 +2122,7 @@
         <v>12</v>
       </c>
       <c r="P32">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q32">
         <v>7</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117339</v>
+        <v>0.606863376011734</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072247</v>
+        <v>0.5270445030072253</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.100653241049135</v>
+        <v>0.1006532410491351</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091508</v>
+        <v>0.05545829422091531</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588712</v>
+        <v>0.001236945685588809</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106635</v>
+        <v>0.06812048270106685</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301354</v>
+        <v>0.01089577315301371</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328441</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328442</v>
+        <v>0.4382144437328441</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602291</v>
+        <v>0.02413727288602327</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409014</v>
+        <v>0.04165861565409022</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579484</v>
+        <v>0.01871153087579565</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194929</v>
+        <v>0.003790535553195104</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127862</v>
+        <v>0.227998432712786</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2874,7 +2874,7 @@
         <v>30</v>
       </c>
       <c r="P46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q46">
         <v>15</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603865</v>
+        <v>0.005298875417604169</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603884</v>
+        <v>0.005298875417604185</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685266</v>
+        <v>0.006905590848685303</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290822</v>
+        <v>0.0340886332729083</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449387</v>
+        <v>0.00214686610044956</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726889</v>
+        <v>0.08230408821726903</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409655</v>
+        <v>0.0002505773915410174</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.121076913323043</v>
+        <v>0.1210769133230432</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850176</v>
+        <v>0.005447925395850289</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738931</v>
+        <v>0.5730798804738926</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3516,7 +3516,7 @@
         <v>23</v>
       </c>
       <c r="P58">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q58">
         <v>11</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652421</v>
+        <v>0.1969762873652423</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3571,7 +3571,7 @@
         <v>11</v>
       </c>
       <c r="P59">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462029</v>
+        <v>0.04986997364462036</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462031</v>
+        <v>0.04986997364462035</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359536</v>
+        <v>0.02452746104359542</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856283</v>
+        <v>0.3552799123856282</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3785,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="P63">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q63">
         <v>14</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422737</v>
+        <v>0.7252640270422738</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -490,7 +490,7 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q2">
         <v>15</v>
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.1979348761526409</v>
+        <v>0.1979348761526411</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -545,7 +545,7 @@
         <v>19</v>
       </c>
       <c r="P3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q3">
         <v>11</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727425</v>
+        <v>0.2056428338727414</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793945209</v>
+        <v>0.003154190793944975</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105854</v>
+        <v>0.01557029016105771</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830192094</v>
+        <v>0.005855458830191564</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600782</v>
+        <v>0.001186184338600617</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333339</v>
+        <v>0.004753484704332928</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704333344</v>
+        <v>0.004753484704332922</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326837039</v>
+        <v>0.002771926326836708</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402844</v>
+        <v>0.4792480623402845</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602328</v>
+        <v>0.02413727288602244</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="P14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q14">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999227</v>
+        <v>0.01091136045999144</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1248,7 +1248,7 @@
         <v>37</v>
       </c>
       <c r="P16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q16">
         <v>15</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089467</v>
+        <v>0.5186239472089458</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462037</v>
+        <v>0.04986997364462032</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594966</v>
+        <v>0.04448123221594959</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578892</v>
+        <v>0.05378569674578786</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235187</v>
+        <v>0.1019516679235185</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999649</v>
+        <v>0.02689303999999544</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326837044</v>
+        <v>0.002771926326836728</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945222</v>
+        <v>0.003154190793944968</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620876</v>
+        <v>0.01468630870620815</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502751</v>
+        <v>0.01130002982502748</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462036</v>
+        <v>0.04986997364462027</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652396</v>
+        <v>0.2852074932652394</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2012,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q30">
         <v>11</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531602</v>
+        <v>0.1556265945531603</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2067,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="P31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q31">
         <v>15</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097576</v>
+        <v>0.1963072587097577</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2122,7 +2122,7 @@
         <v>12</v>
       </c>
       <c r="P32">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32">
         <v>7</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.606863376011734</v>
+        <v>0.6068633760117336</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.1006532410491351</v>
+        <v>0.1006532410491349</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091531</v>
+        <v>0.05545829422091468</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588809</v>
+        <v>0.001236945685588678</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106685</v>
+        <v>0.06812048270106567</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301371</v>
+        <v>0.01089577315301337</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328441</v>
+        <v>0.4382144437328444</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328441</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602327</v>
+        <v>0.02413727288602244</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409022</v>
+        <v>0.04165861565408997</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579565</v>
+        <v>0.01871153087579451</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553195104</v>
+        <v>0.003790535553194743</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.227998432712786</v>
+        <v>0.2279984327127861</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2874,7 +2874,7 @@
         <v>30</v>
       </c>
       <c r="P46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q46">
         <v>15</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417604169</v>
+        <v>0.005298875417603598</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417604185</v>
+        <v>0.005298875417603599</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685303</v>
+        <v>0.006905590848685305</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.0340886332729083</v>
+        <v>0.03408863327290833</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.00214686610044956</v>
+        <v>0.002146866100449262</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726903</v>
+        <v>0.08230408821726891</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915410174</v>
+        <v>0.0002505773915409962</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230432</v>
+        <v>0.1210769133230429</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850289</v>
+        <v>0.00544792539585</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738926</v>
+        <v>0.5730798804738922</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.161368919454233</v>
+        <v>0.1613689194542331</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3516,7 +3516,7 @@
         <v>23</v>
       </c>
       <c r="P58">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q58">
         <v>11</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652423</v>
+        <v>0.196976287365242</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3571,7 +3571,7 @@
         <v>11</v>
       </c>
       <c r="P59">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462036</v>
+        <v>0.04986997364462028</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462035</v>
+        <v>0.04986997364462025</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359542</v>
+        <v>0.02452746104359533</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856282</v>
+        <v>0.3552799123856283</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3785,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="P63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q63">
         <v>14</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422738</v>
+        <v>0.7252640270422736</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340304</v>
+        <v>0.1627043167340305</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.1979348761526411</v>
+        <v>0.197934876152641</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727414</v>
+        <v>0.2056428338727417</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793944975</v>
+        <v>0.00315419079394504</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105771</v>
+        <v>0.01557029016105786</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191564</v>
+        <v>0.005855458830191642</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600617</v>
+        <v>0.001186184338600657</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704332928</v>
+        <v>0.004753484704333033</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704332922</v>
+        <v>0.004753484704333006</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836708</v>
+        <v>0.002771926326836769</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602244</v>
+        <v>0.02413727288602266</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451341</v>
+        <v>0.2745492459451342</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999144</v>
+        <v>0.01091136045999156</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089458</v>
+        <v>0.5186239472089464</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462032</v>
+        <v>0.04986997364462031</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594959</v>
+        <v>0.04448123221594952</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578786</v>
+        <v>0.0537856967457881</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999544</v>
+        <v>0.02689303999999563</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836728</v>
+        <v>0.002771926326836755</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793944968</v>
+        <v>0.003154190793945047</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620815</v>
+        <v>0.01468630870620835</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502748</v>
+        <v>0.01130002982502741</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502749</v>
+        <v>0.01130002982502743</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462027</v>
+        <v>0.04986997364462028</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652394</v>
+        <v>0.2852074932652393</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531603</v>
+        <v>0.1556265945531604</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097577</v>
+        <v>0.1963072587097576</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117336</v>
+        <v>0.6068633760117339</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091468</v>
+        <v>0.05545829422091488</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588678</v>
+        <v>0.001236945685588624</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106567</v>
+        <v>0.06812048270106599</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301337</v>
+        <v>0.01089577315301349</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328442</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602244</v>
+        <v>0.02413727288602262</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565408997</v>
+        <v>0.04165861565409001</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579451</v>
+        <v>0.01871153087579469</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194743</v>
+        <v>0.003790535553194842</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127861</v>
+        <v>0.2279984327127864</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603598</v>
+        <v>0.005298875417603719</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603599</v>
+        <v>0.005298875417603733</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685305</v>
+        <v>0.006905590848685274</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290833</v>
+        <v>0.03408863327290823</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449262</v>
+        <v>0.002146866100449326</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726891</v>
+        <v>0.08230408821726889</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409962</v>
+        <v>0.0002505773915409442</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.00544792539585</v>
+        <v>0.005447925395850077</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738922</v>
+        <v>0.573079880473893</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958986</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.196976287365242</v>
+        <v>0.1969762873652422</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462028</v>
+        <v>0.04986997364462026</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462025</v>
+        <v>0.04986997364462027</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422736</v>
+        <v>0.7252640270422737</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340305</v>
+        <v>0.1627043167340307</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -490,7 +490,7 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q2">
         <v>15</v>
@@ -545,7 +545,7 @@
         <v>19</v>
       </c>
       <c r="P3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q3">
         <v>11</v>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.00315419079394504</v>
+        <v>0.003154190793945048</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105786</v>
+        <v>0.01557029016105788</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191642</v>
+        <v>0.005855458830191703</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600657</v>
+        <v>0.001186184338600673</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333033</v>
+        <v>0.004753484704332996</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704333006</v>
+        <v>0.004753484704333011</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836769</v>
+        <v>0.002771926326836805</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402845</v>
+        <v>0.4792480623402843</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602266</v>
+        <v>0.02413727288602276</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="P14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q14">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999156</v>
+        <v>0.01091136045999166</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1248,7 +1248,7 @@
         <v>37</v>
       </c>
       <c r="P16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q16">
         <v>15</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089464</v>
+        <v>0.5186239472089469</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462031</v>
+        <v>0.04986997364462028</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594952</v>
+        <v>0.04448123221594961</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.0537856967457881</v>
+        <v>0.05378569674578808</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999563</v>
+        <v>0.02689303999999577</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836755</v>
+        <v>0.0027719263268368</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945047</v>
+        <v>0.003154190793945046</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620835</v>
+        <v>0.01468630870620827</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502741</v>
+        <v>0.01130002982502749</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502743</v>
+        <v>0.01130002982502747</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652393</v>
+        <v>0.2852074932652392</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2012,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="P30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>11</v>
@@ -2067,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="P31">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q31">
         <v>15</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097576</v>
+        <v>0.1963072587097577</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2122,7 +2122,7 @@
         <v>12</v>
       </c>
       <c r="P32">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q32">
         <v>7</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117339</v>
+        <v>0.606863376011734</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072253</v>
+        <v>0.5270445030072252</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.1006532410491349</v>
+        <v>0.100653241049135</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091488</v>
+        <v>0.0554582942209149</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588624</v>
+        <v>0.001236945685588668</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106599</v>
+        <v>0.06812048270106603</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301349</v>
+        <v>0.01089577315301348</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328444</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328442</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602262</v>
+        <v>0.02413727288602272</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409001</v>
+        <v>0.04165861565409002</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579469</v>
+        <v>0.01871153087579458</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194842</v>
+        <v>0.003790535553194827</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127864</v>
+        <v>0.2279984327127862</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2874,7 +2874,7 @@
         <v>30</v>
       </c>
       <c r="P46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q46">
         <v>15</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603719</v>
+        <v>0.005298875417603761</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603733</v>
+        <v>0.005298875417603759</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685274</v>
+        <v>0.006905590848685281</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290823</v>
+        <v>0.0340886332729083</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449326</v>
+        <v>0.002146866100449344</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726889</v>
+        <v>0.08230408821726892</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409442</v>
+        <v>0.0002505773915409855</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54">
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850077</v>
+        <v>0.005447925395850105</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56">
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958986</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3516,7 +3516,7 @@
         <v>23</v>
       </c>
       <c r="P58">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q58">
         <v>11</v>
@@ -3571,7 +3571,7 @@
         <v>11</v>
       </c>
       <c r="P59">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462027</v>
+        <v>0.04986997364462028</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359533</v>
+        <v>0.02452746104359532</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856283</v>
+        <v>0.3552799123856284</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3785,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="P63">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q63">
         <v>14</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422737</v>
+        <v>0.725264027042274</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340307</v>
+        <v>0.1627043167340303</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -490,7 +490,7 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q2">
         <v>15</v>
@@ -545,7 +545,7 @@
         <v>19</v>
       </c>
       <c r="P3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q3">
         <v>11</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727417</v>
+        <v>0.2056428338727415</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793945048</v>
+        <v>0.003154190793944966</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105788</v>
+        <v>0.01557029016105776</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191703</v>
+        <v>0.005855458830191627</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600673</v>
+        <v>0.001186184338600625</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704332996</v>
+        <v>0.004753484704332904</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704333011</v>
+        <v>0.004753484704332898</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836805</v>
+        <v>0.002771926326836723</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402843</v>
+        <v>0.4792480623402845</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602276</v>
+        <v>0.02413727288602256</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451342</v>
+        <v>0.2745492459451344</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="P14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q14">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999166</v>
+        <v>0.01091136045999148</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958986</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1248,7 +1248,7 @@
         <v>37</v>
       </c>
       <c r="P16">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q16">
         <v>15</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089469</v>
+        <v>0.5186239472089461</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462028</v>
+        <v>0.04986997364462018</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594961</v>
+        <v>0.0444812322159496</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578808</v>
+        <v>0.05378569674578786</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235185</v>
+        <v>0.1019516679235184</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999577</v>
+        <v>0.02689303999999556</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.0027719263268368</v>
+        <v>0.00277192632683671</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945046</v>
+        <v>0.00315419079394496</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620827</v>
+        <v>0.01468630870620813</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502749</v>
+        <v>0.01130002982502746</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462028</v>
+        <v>0.04986997364462021</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -2012,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q30">
         <v>11</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531604</v>
+        <v>0.1556265945531602</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2067,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="P31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q31">
         <v>15</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097577</v>
+        <v>0.1963072587097576</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2122,7 +2122,7 @@
         <v>12</v>
       </c>
       <c r="P32">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32">
         <v>7</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.606863376011734</v>
+        <v>0.6068633760117338</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.100653241049135</v>
+        <v>0.1006532410491349</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.0554582942209149</v>
+        <v>0.05545829422091472</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588668</v>
+        <v>0.001236945685588678</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106603</v>
+        <v>0.06812048270106584</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301348</v>
+        <v>0.01089577315301339</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328441</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2556,7 +2556,7 @@
         <v>24</v>
       </c>
       <c r="P40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>14</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328441</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602272</v>
+        <v>0.02413727288602257</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409002</v>
+        <v>0.04165861565408995</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579458</v>
+        <v>0.01871153087579461</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194827</v>
+        <v>0.003790535553194719</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127862</v>
+        <v>0.2279984327127861</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2874,7 +2874,7 @@
         <v>30</v>
       </c>
       <c r="P46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q46">
         <v>15</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603761</v>
+        <v>0.005298875417603626</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603759</v>
+        <v>0.005298875417603636</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685281</v>
+        <v>0.006905590848685298</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.0340886332729083</v>
+        <v>0.03408863327290828</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449344</v>
+        <v>0.002146866100449302</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726892</v>
+        <v>0.08230408821726885</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409855</v>
+        <v>0.0002505773915409902</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230429</v>
+        <v>0.1210769133230428</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850105</v>
+        <v>0.005447925395850016</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.573079880473893</v>
+        <v>0.5730798804738926</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542331</v>
+        <v>0.161368919454233</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3516,7 +3516,7 @@
         <v>23</v>
       </c>
       <c r="P58">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q58">
         <v>11</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652422</v>
+        <v>0.196976287365242</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3571,7 +3571,7 @@
         <v>11</v>
       </c>
       <c r="P59">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462026</v>
+        <v>0.04986997364462018</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462028</v>
+        <v>0.0498699736446202</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359532</v>
+        <v>0.0245274610435953</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
@@ -3785,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="P63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q63">
         <v>14</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.725264027042274</v>
+        <v>0.7252640270422732</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340303</v>
+        <v>0.1627043167340306</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.197934876152641</v>
+        <v>0.1979348761526409</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727415</v>
+        <v>0.2056428338727421</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793944966</v>
+        <v>0.003154190793945086</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105776</v>
+        <v>0.01557029016105806</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191627</v>
+        <v>0.005855458830191841</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600625</v>
+        <v>0.001186184338600699</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704332904</v>
+        <v>0.004753484704333105</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704332898</v>
+        <v>0.00475348470433311</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836723</v>
+        <v>0.002771926326836871</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402845</v>
+        <v>0.4792480623402844</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602256</v>
+        <v>0.02413727288602285</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451344</v>
+        <v>0.2745492459451342</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999148</v>
+        <v>0.01091136045999184</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958986</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1248,7 +1248,7 @@
         <v>37</v>
       </c>
       <c r="P16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q16">
         <v>15</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089461</v>
+        <v>0.5186239472089462</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462018</v>
+        <v>0.04986997364462026</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.0444812322159496</v>
+        <v>0.04448123221594961</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578786</v>
+        <v>0.05378569674578833</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235184</v>
+        <v>0.1019516679235186</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999556</v>
+        <v>0.02689303999999591</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.00277192632683671</v>
+        <v>0.002771926326836876</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.00315419079394496</v>
+        <v>0.003154190793945101</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620813</v>
+        <v>0.01468630870620845</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502746</v>
+        <v>0.01130002982502747</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462021</v>
+        <v>0.04986997364462031</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652392</v>
+        <v>0.2852074932652393</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531602</v>
+        <v>0.1556265945531604</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117338</v>
+        <v>0.606863376011734</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072252</v>
+        <v>0.5270445030072253</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.1006532410491349</v>
+        <v>0.100653241049135</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091472</v>
+        <v>0.05545829422091499</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588678</v>
+        <v>0.001236945685588708</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106584</v>
+        <v>0.06812048270106619</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301339</v>
+        <v>0.01089577315301354</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -2556,7 +2556,7 @@
         <v>24</v>
       </c>
       <c r="P40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>14</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602257</v>
+        <v>0.02413727288602285</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565408995</v>
+        <v>0.04165861565409009</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579461</v>
+        <v>0.01871153087579488</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194719</v>
+        <v>0.003790535553194921</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127861</v>
+        <v>0.227998432712786</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603626</v>
+        <v>0.005298875417603875</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603636</v>
+        <v>0.005298875417603836</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685298</v>
+        <v>0.006905590848685272</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290828</v>
+        <v>0.03408863327290829</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449302</v>
+        <v>0.00214686610044937</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726885</v>
+        <v>0.08230408821726901</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409902</v>
+        <v>0.0002505773915409691</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230428</v>
+        <v>0.1210769133230429</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850016</v>
+        <v>0.005447925395850156</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738926</v>
+        <v>0.5730798804738922</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.161368919454233</v>
+        <v>0.1613689194542332</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.196976287365242</v>
+        <v>0.1969762873652421</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462018</v>
+        <v>0.04986997364462031</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.0498699736446202</v>
+        <v>0.04986997364462031</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.0245274610435953</v>
+        <v>0.02452746104359537</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856284</v>
+        <v>0.3552799123856283</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422732</v>
+        <v>0.7252640270422738</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340306</v>
+        <v>0.1627043167340304</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.1979348761526409</v>
+        <v>0.1979348761526408</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727421</v>
+        <v>0.205642833872741</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793945086</v>
+        <v>0.003154190793944927</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105806</v>
+        <v>0.01557029016105736</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191841</v>
+        <v>0.005855458830191308</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600699</v>
+        <v>0.001186184338600554</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333105</v>
+        <v>0.004753484704332787</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.00475348470433311</v>
+        <v>0.00475348470433279</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836871</v>
+        <v>0.002771926326836591</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402844</v>
+        <v>0.4792480623402845</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602285</v>
+        <v>0.02413727288602237</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451342</v>
+        <v>0.2745492459451345</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999184</v>
+        <v>0.01091136045999113</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089462</v>
+        <v>0.5186239472089461</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462026</v>
+        <v>0.0498699736446201</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594961</v>
+        <v>0.04448123221594937</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578833</v>
+        <v>0.05378569674578765</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235186</v>
+        <v>0.1019516679235183</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999591</v>
+        <v>0.02689303999999516</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836876</v>
+        <v>0.002771926326836583</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945101</v>
+        <v>0.003154190793944929</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620845</v>
+        <v>0.01468630870620808</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502747</v>
+        <v>0.01130002982502726</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502747</v>
+        <v>0.01130002982502726</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462031</v>
+        <v>0.0498699736446201</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652393</v>
+        <v>0.2852074932652392</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531604</v>
+        <v>0.1556265945531601</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097576</v>
+        <v>0.1963072587097571</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.606863376011734</v>
+        <v>0.606863376011733</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.100653241049135</v>
+        <v>0.1006532410491348</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091499</v>
+        <v>0.05545829422091468</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588708</v>
+        <v>0.001236945685588485</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106619</v>
+        <v>0.06812048270106548</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301354</v>
+        <v>0.01089577315301335</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328441</v>
+        <v>0.4382144437328442</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2556,7 +2556,7 @@
         <v>24</v>
       </c>
       <c r="P40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>14</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328441</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602285</v>
+        <v>0.02413727288602236</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409009</v>
+        <v>0.04165861565408994</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579488</v>
+        <v>0.01871153087579394</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194921</v>
+        <v>0.003790535553194754</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.227998432712786</v>
+        <v>0.2279984327127861</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603875</v>
+        <v>0.005298875417603437</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603836</v>
+        <v>0.005298875417603478</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685272</v>
+        <v>0.006905590848685199</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290829</v>
+        <v>0.03408863327290812</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.00214686610044937</v>
+        <v>0.002146866100449132</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726901</v>
+        <v>0.08230408821726884</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409691</v>
+        <v>0.0002505773915408804</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230429</v>
+        <v>0.1210769133230426</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850156</v>
+        <v>0.005447925395849985</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738922</v>
+        <v>0.5730798804738926</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542332</v>
+        <v>0.1613689194542329</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652421</v>
+        <v>0.1969762873652419</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462031</v>
+        <v>0.04986997364462013</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462031</v>
+        <v>0.04986997364462008</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359537</v>
+        <v>0.02452746104359526</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856283</v>
+        <v>0.3552799123856281</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422738</v>
+        <v>0.7252640270422734</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340304</v>
+        <v>0.1627043167340305</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.1979348761526408</v>
+        <v>0.1979348761526409</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.205642833872741</v>
+        <v>0.2056428338727417</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793944927</v>
+        <v>0.003154190793944998</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105736</v>
+        <v>0.01557029016105786</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191308</v>
+        <v>0.005855458830191595</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600554</v>
+        <v>0.00118618433860063</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704332787</v>
+        <v>0.004753484704332988</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.00475348470433279</v>
+        <v>0.004753484704332992</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836591</v>
+        <v>0.002771926326836745</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402845</v>
+        <v>0.4792480623402849</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602237</v>
+        <v>0.02413727288602265</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451345</v>
+        <v>0.2745492459451342</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999113</v>
+        <v>0.01091136045999157</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089461</v>
+        <v>0.5186239472089463</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.0498699736446201</v>
+        <v>0.04986997364462027</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594937</v>
+        <v>0.04448123221594958</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578765</v>
+        <v>0.05378569674578811</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235183</v>
+        <v>0.1019516679235185</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999516</v>
+        <v>0.02689303999999573</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836583</v>
+        <v>0.00277192632683674</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793944929</v>
+        <v>0.003154190793945009</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620808</v>
+        <v>0.01468630870620828</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502726</v>
+        <v>0.01130002982502747</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502726</v>
+        <v>0.01130002982502743</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.0498699736446201</v>
+        <v>0.04986997364462026</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652392</v>
+        <v>0.2852074932652393</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531601</v>
+        <v>0.1556265945531602</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097571</v>
+        <v>0.1963072587097577</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.606863376011733</v>
+        <v>0.6068633760117337</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072253</v>
+        <v>0.5270445030072254</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.1006532410491348</v>
+        <v>0.100653241049135</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091468</v>
+        <v>0.05545829422091485</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588485</v>
+        <v>0.001236945685588638</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106548</v>
+        <v>0.06812048270106598</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301335</v>
+        <v>0.01089577315301346</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328442</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2556,7 +2556,7 @@
         <v>24</v>
       </c>
       <c r="P40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>14</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328441</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602236</v>
+        <v>0.02413727288602262</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565408994</v>
+        <v>0.04165861565409005</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579394</v>
+        <v>0.01871153087579471</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194754</v>
+        <v>0.003790535553194817</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127861</v>
+        <v>0.2279984327127862</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603437</v>
+        <v>0.005298875417603719</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603478</v>
+        <v>0.005298875417603712</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685199</v>
+        <v>0.00690559084868529</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290812</v>
+        <v>0.03408863327290829</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449132</v>
+        <v>0.002146866100449335</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726884</v>
+        <v>0.08230408821726894</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915408804</v>
+        <v>0.0002505773915409558</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230426</v>
+        <v>0.121076913323043</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395849985</v>
+        <v>0.005447925395850077</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738926</v>
+        <v>0.5730798804738927</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542329</v>
+        <v>0.161368919454233</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652419</v>
+        <v>0.1969762873652422</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462013</v>
+        <v>0.04986997364462025</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462008</v>
+        <v>0.04986997364462025</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359526</v>
+        <v>0.02452746104359534</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856281</v>
+        <v>0.3552799123856282</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422734</v>
+        <v>0.7252640270422739</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.1979348761526409</v>
+        <v>0.197934876152641</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727417</v>
+        <v>0.2056428338727419</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793944998</v>
+        <v>0.003154190793945116</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105786</v>
+        <v>0.01557029016105826</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191595</v>
+        <v>0.005855458830191979</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.00118618433860063</v>
+        <v>0.001186184338600735</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704332988</v>
+        <v>0.004753484704333249</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704332992</v>
+        <v>0.004753484704333214</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836745</v>
+        <v>0.002771926326836918</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402849</v>
+        <v>0.4792480623402843</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602265</v>
+        <v>0.02413727288602291</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999157</v>
+        <v>0.01091136045999198</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089463</v>
+        <v>0.5186239472089462</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462027</v>
+        <v>0.04986997364462038</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594958</v>
+        <v>0.04448123221594981</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578811</v>
+        <v>0.05378569674578851</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235185</v>
+        <v>0.1019516679235186</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999573</v>
+        <v>0.02689303999999606</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.00277192632683674</v>
+        <v>0.002771926326836936</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945009</v>
+        <v>0.003154190793945119</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620828</v>
+        <v>0.01468630870620855</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502747</v>
+        <v>0.01130002982502761</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502743</v>
+        <v>0.01130002982502762</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462026</v>
+        <v>0.04986997364462038</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652393</v>
+        <v>0.2852074932652395</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097577</v>
+        <v>0.1963072587097578</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117337</v>
+        <v>0.6068633760117331</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072254</v>
+        <v>0.5270445030072251</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.100653241049135</v>
+        <v>0.1006532410491351</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091485</v>
+        <v>0.05545829422091505</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588638</v>
+        <v>0.00123694568558879</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106598</v>
+        <v>0.06812048270106631</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301346</v>
+        <v>0.01089577315301356</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328442</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602262</v>
+        <v>0.02413727288602291</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409005</v>
+        <v>0.04165861565409007</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579471</v>
+        <v>0.01871153087579526</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194817</v>
+        <v>0.003790535553194958</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603719</v>
+        <v>0.005298875417604045</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603712</v>
+        <v>0.005298875417604052</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.00690559084868529</v>
+        <v>0.006905590848685359</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290829</v>
+        <v>0.0340886332729084</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449335</v>
+        <v>0.002146866100449504</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726894</v>
+        <v>0.08230408821726903</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409558</v>
+        <v>0.000250577391541028</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.121076913323043</v>
+        <v>0.1210769133230431</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850077</v>
+        <v>0.005447925395850176</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738927</v>
+        <v>0.5730798804738926</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.161368919454233</v>
+        <v>0.1613689194542331</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652422</v>
+        <v>0.1969762873652423</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462025</v>
+        <v>0.04986997364462033</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462025</v>
+        <v>0.04986997364462036</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359534</v>
+        <v>0.0245274610435954</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856282</v>
+        <v>0.3552799123856281</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422739</v>
+        <v>0.7252640270422737</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340305</v>
+        <v>0.1627043167340307</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -490,7 +490,7 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q2">
         <v>15</v>
@@ -545,7 +545,7 @@
         <v>19</v>
       </c>
       <c r="P3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q3">
         <v>11</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727419</v>
+        <v>0.2056428338727414</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793945116</v>
+        <v>0.003154190793945008</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105826</v>
+        <v>0.01557029016105772</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191979</v>
+        <v>0.005855458830191595</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600735</v>
+        <v>0.001186184338600646</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333249</v>
+        <v>0.004753484704332964</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704333214</v>
+        <v>0.004753484704332943</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836918</v>
+        <v>0.002771926326836709</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402843</v>
+        <v>0.4792480623402849</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602291</v>
+        <v>0.02413727288602255</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451342</v>
+        <v>0.2745492459451345</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="P14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q14">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999198</v>
+        <v>0.0109113604599915</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089462</v>
+        <v>0.5186239472089466</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462038</v>
+        <v>0.0498699736446203</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1358,7 +1358,7 @@
         <v>37</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q18">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.04448123221594981</v>
+        <v>0.0444812322159496</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578851</v>
+        <v>0.05378569674578784</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235186</v>
+        <v>0.1019516679235184</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999606</v>
+        <v>0.02689303999999549</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836936</v>
+        <v>0.002771926326836727</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945119</v>
+        <v>0.003154190793945</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620855</v>
+        <v>0.01468630870620821</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502761</v>
+        <v>0.01130002982502749</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502762</v>
+        <v>0.0113000298250275</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462038</v>
+        <v>0.04986997364462031</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652395</v>
+        <v>0.2852074932652394</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2012,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="P30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>11</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531602</v>
+        <v>0.1556265945531603</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2067,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="P31">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q31">
         <v>15</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097578</v>
+        <v>0.1963072587097576</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2122,7 +2122,7 @@
         <v>12</v>
       </c>
       <c r="P32">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q32">
         <v>7</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117331</v>
+        <v>0.6068633760117338</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072251</v>
+        <v>0.5270445030072255</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.1006532410491351</v>
+        <v>0.100653241049135</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091505</v>
+        <v>0.05545829422091481</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.00123694568558879</v>
+        <v>0.001236945685588652</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106631</v>
+        <v>0.06812048270106576</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301356</v>
+        <v>0.01089577315301342</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328442</v>
+        <v>0.4382144437328446</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328441</v>
+        <v>0.4382144437328446</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602291</v>
+        <v>0.02413727288602253</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409007</v>
+        <v>0.04165861565409006</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579526</v>
+        <v>0.01871153087579443</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194958</v>
+        <v>0.003790535553194825</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46">
@@ -2874,7 +2874,7 @@
         <v>30</v>
       </c>
       <c r="P46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q46">
         <v>15</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417604045</v>
+        <v>0.00529887541760369</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417604052</v>
+        <v>0.005298875417603645</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685359</v>
+        <v>0.006905590848685294</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.0340886332729084</v>
+        <v>0.03408863327290827</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449504</v>
+        <v>0.002146866100449276</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726903</v>
+        <v>0.08230408821726898</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.000250577391541028</v>
+        <v>0.0002505773915409678</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230431</v>
+        <v>0.1210769133230429</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850176</v>
+        <v>0.005447925395850053</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738926</v>
+        <v>0.573079880473893</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542331</v>
+        <v>0.1613689194542332</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3516,7 +3516,7 @@
         <v>23</v>
       </c>
       <c r="P58">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q58">
         <v>11</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652423</v>
+        <v>0.1969762873652422</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3571,7 +3571,7 @@
         <v>11</v>
       </c>
       <c r="P59">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462033</v>
+        <v>0.04986997364462029</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462036</v>
+        <v>0.04986997364462027</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.0245274610435954</v>
+        <v>0.02452746104359532</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856281</v>
+        <v>0.355279912385628</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3785,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="P63">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q63">
         <v>14</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422737</v>
+        <v>0.7252640270422738</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340307</v>
+        <v>0.1627043167340305</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -490,7 +490,7 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q2">
         <v>15</v>
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.197934876152641</v>
+        <v>0.1979348761526409</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -545,7 +545,7 @@
         <v>19</v>
       </c>
       <c r="P3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q3">
         <v>11</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727414</v>
+        <v>0.2056428338727423</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793945008</v>
+        <v>0.003154190793945193</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105772</v>
+        <v>0.01557029016105841</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191595</v>
+        <v>0.00585545883019204</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600646</v>
+        <v>0.001186184338600763</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704332964</v>
+        <v>0.004753484704333313</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -863,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q9">
         <v>15</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704332943</v>
+        <v>0.004753484704333295</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836709</v>
+        <v>0.002771926326837001</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402849</v>
+        <v>0.4792480623402844</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602255</v>
+        <v>0.02413727288602316</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451345</v>
+        <v>0.2745492459451342</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="P14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q14">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.0109113604599915</v>
+        <v>0.01091136045999216</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.0498699736446203</v>
+        <v>0.04986997364462042</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.0444812322159496</v>
+        <v>0.0444812322159497</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578784</v>
+        <v>0.05378569674578873</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235184</v>
+        <v>0.1019516679235188</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999549</v>
+        <v>0.02689303999999634</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836727</v>
+        <v>0.002771926326837011</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945</v>
+        <v>0.003154190793945212</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620821</v>
+        <v>0.01468630870620875</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502749</v>
+        <v>0.01130002982502752</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.0113000298250275</v>
+        <v>0.01130002982502752</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462031</v>
+        <v>0.04986997364462039</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652394</v>
+        <v>0.2852074932652395</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2012,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q30">
         <v>11</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531603</v>
+        <v>0.1556265945531604</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2067,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="P31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q31">
         <v>15</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097576</v>
+        <v>0.1963072587097577</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2122,7 +2122,7 @@
         <v>12</v>
       </c>
       <c r="P32">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32">
         <v>7</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072255</v>
+        <v>0.5270445030072253</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2287,7 +2287,7 @@
         <v>21</v>
       </c>
       <c r="P35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q35">
         <v>11</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091481</v>
+        <v>0.05545829422091521</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2342,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="P36">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q36">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588652</v>
+        <v>0.001236945685588759</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106576</v>
+        <v>0.06812048270106663</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2452,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="P38">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q38">
         <v>12</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301342</v>
+        <v>0.01089577315301365</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328446</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2556,7 +2556,7 @@
         <v>24</v>
       </c>
       <c r="P40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>14</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328446</v>
+        <v>0.4382144437328443</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602253</v>
+        <v>0.02413727288602314</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409006</v>
+        <v>0.04165861565409022</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579443</v>
+        <v>0.01871153087579536</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194825</v>
+        <v>0.003790535553195053</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127862</v>
+        <v>0.2279984327127861</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2874,7 +2874,7 @@
         <v>30</v>
       </c>
       <c r="P46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q46">
         <v>15</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.00529887541760369</v>
+        <v>0.005298875417604109</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603645</v>
+        <v>0.005298875417604102</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685294</v>
+        <v>0.006905590848685293</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449276</v>
+        <v>0.002146866100449527</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726898</v>
+        <v>0.08230408821726896</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3198,7 +3198,7 @@
         <v>34</v>
       </c>
       <c r="P52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q52">
         <v>15</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409678</v>
+        <v>0.0002505773915409981</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230429</v>
+        <v>0.1210769133230431</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="P54">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850053</v>
+        <v>0.005447925395850287</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.573079880473893</v>
+        <v>0.5730798804738925</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3461,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="P57">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q57">
         <v>15</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542332</v>
+        <v>0.1613689194542331</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3516,7 +3516,7 @@
         <v>23</v>
       </c>
       <c r="P58">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q58">
         <v>11</v>
@@ -3571,7 +3571,7 @@
         <v>11</v>
       </c>
       <c r="P59">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462029</v>
+        <v>0.04986997364462038</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3626,7 +3626,7 @@
         <v>37</v>
       </c>
       <c r="P60">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q60">
         <v>15</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462027</v>
+        <v>0.04986997364462037</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.02452746104359532</v>
+        <v>0.0245274610435954</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.355279912385628</v>
+        <v>0.3552799123856283</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3785,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="P63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q63">
         <v>14</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422738</v>
+        <v>0.7252640270422737</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727423</v>
+        <v>0.2056428338727415</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793945193</v>
+        <v>0.003154190793944947</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.01557029016105841</v>
+        <v>0.0155702901610576</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.00585545883019204</v>
+        <v>0.005855458830191469</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -759,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600763</v>
+        <v>0.001186184338600587</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704333313</v>
+        <v>0.004753484704332893</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704333295</v>
+        <v>0.004753484704332894</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="P10">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326837001</v>
+        <v>0.002771926326836643</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402844</v>
+        <v>0.4792480623402846</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602316</v>
+        <v>0.02413727288602254</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451342</v>
+        <v>0.2745492459451345</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999216</v>
+        <v>0.01091136045999133</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958989</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089466</v>
+        <v>0.5186239472089468</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.04986997364462042</v>
+        <v>0.0498699736446202</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.0444812322159497</v>
+        <v>0.0444812322159495</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1413,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="P19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q19">
         <v>11</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578873</v>
+        <v>0.05378569674578782</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235188</v>
+        <v>0.1019516679235184</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999634</v>
+        <v>0.02689303999999549</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1578,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="P22">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326837011</v>
+        <v>0.002771926326836644</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.003154190793945212</v>
+        <v>0.00315419079394494</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1707,7 +1707,7 @@
         <v>0.3024390243902439</v>
       </c>
       <c r="F25">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0.2311387471655328</v>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.01468630870620875</v>
+        <v>0.0146863087062081</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
       <c r="P26">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>15</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502752</v>
+        <v>0.01130002982502739</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502752</v>
+        <v>0.01130002982502737</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.04986997364462039</v>
+        <v>0.0498699736446202</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652395</v>
+        <v>0.2852074932652392</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531604</v>
+        <v>0.1556265945531603</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097577</v>
+        <v>0.1963072587097576</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117338</v>
+        <v>0.6068633760117337</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072253</v>
+        <v>0.5270445030072252</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2257,7 +2257,7 @@
         <v>0.2421875</v>
       </c>
       <c r="F35">
-        <v>0.100653241049135</v>
+        <v>0.1006532410491349</v>
       </c>
       <c r="G35">
         <v>0.4822530864197531</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091521</v>
+        <v>0.05545829422091476</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588759</v>
+        <v>0.001236945685588575</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106663</v>
+        <v>0.06812048270106578</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301365</v>
+        <v>0.01089577315301338</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2504,7 +2504,7 @@
         <v>39</v>
       </c>
       <c r="P39">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
@@ -2526,7 +2526,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F40">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328442</v>
       </c>
       <c r="G40">
         <v>0.5292881944444444</v>
@@ -2556,7 +2556,7 @@
         <v>24</v>
       </c>
       <c r="P40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>14</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328443</v>
+        <v>0.4382144437328441</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="P41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q41">
         <v>14</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602314</v>
+        <v>0.02413727288602258</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565409022</v>
+        <v>0.04165861565408996</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>39</v>
       </c>
       <c r="P43">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579536</v>
+        <v>0.01871153087579441</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553195053</v>
+        <v>0.003790535553194765</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>39</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46">
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127861</v>
+        <v>0.2279984327127862</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417604109</v>
+        <v>0.005298875417603563</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417604102</v>
+        <v>0.005298875417603584</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685293</v>
+        <v>0.006905590848685265</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>39</v>
       </c>
       <c r="P49">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449527</v>
+        <v>0.002146866100449228</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3143,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="P51">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726896</v>
+        <v>0.08230408821726883</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409981</v>
+        <v>0.0002505773915409316</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="P53">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230431</v>
+        <v>0.1210769133230428</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850287</v>
+        <v>0.005447925395850025</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>39</v>
       </c>
       <c r="P55">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738925</v>
+        <v>0.5730798804738928</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958987</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542331</v>
+        <v>0.1613689194542328</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3541,7 +3541,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F59">
-        <v>0.1969762873652422</v>
+        <v>0.1969762873652421</v>
       </c>
       <c r="G59">
         <v>0.3472222222222222</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462038</v>
+        <v>0.04986997364462016</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462037</v>
+        <v>0.04986997364462019</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="P61">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q61">
         <v>15</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.0245274610435954</v>
+        <v>0.0245274610435953</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>39</v>
       </c>
       <c r="P62">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856283</v>
+        <v>0.3552799123856286</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422737</v>
+        <v>0.7252640270422739</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>

--- a/output/pharma_nordic_example_centralitymetrics.xlsx
+++ b/output/pharma_nordic_example_centralitymetrics.xlsx
@@ -460,7 +460,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F2">
-        <v>0.1627043167340305</v>
+        <v>0.1627043167340306</v>
       </c>
       <c r="G2">
         <v>0.6566840277777779</v>
@@ -515,7 +515,7 @@
         <v>0.223826714801444</v>
       </c>
       <c r="F3">
-        <v>0.1979348761526409</v>
+        <v>0.197934876152641</v>
       </c>
       <c r="G3">
         <v>0.4583333333333333</v>
@@ -570,7 +570,7 @@
         <v>0.3625730994152047</v>
       </c>
       <c r="F4">
-        <v>0.2056428338727415</v>
+        <v>0.2056428338727417</v>
       </c>
       <c r="G4">
         <v>0.1773469387755102</v>
@@ -625,7 +625,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F5">
-        <v>0.003154190793944947</v>
+        <v>0.003154190793945042</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -652,7 +652,7 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         <v>0.2683982683982684</v>
       </c>
       <c r="F6">
-        <v>0.0155702901610576</v>
+        <v>0.01557029016105794</v>
       </c>
       <c r="G6">
         <v>0.2401</v>
@@ -729,7 +729,7 @@
         <v>0.223021582733813</v>
       </c>
       <c r="F7">
-        <v>0.005855458830191469</v>
+        <v>0.005855458830191706</v>
       </c>
       <c r="G7">
         <v>0.305</v>
@@ -784,7 +784,7 @@
         <v>0.1828908554572271</v>
       </c>
       <c r="F8">
-        <v>0.001186184338600587</v>
+        <v>0.00118618433860067</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -833,7 +833,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F9">
-        <v>0.004753484704332893</v>
+        <v>0.004753484704333055</v>
       </c>
       <c r="G9">
         <v>0.8890306122448979</v>
@@ -888,7 +888,7 @@
         <v>0.2052980132450331</v>
       </c>
       <c r="F10">
-        <v>0.004753484704332894</v>
+        <v>0.004753484704333059</v>
       </c>
       <c r="G10">
         <v>0.8890306122448979</v>
@@ -943,7 +943,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F11">
-        <v>0.002771926326836643</v>
+        <v>0.002771926326836808</v>
       </c>
       <c r="G11">
         <v>0.9225</v>
@@ -973,7 +973,7 @@
         <v>38</v>
       </c>
       <c r="P11">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q11">
         <v>15</v>
@@ -998,7 +998,7 @@
         <v>0.248</v>
       </c>
       <c r="F12">
-        <v>0.4792480623402846</v>
+        <v>0.4792480623402844</v>
       </c>
       <c r="G12">
         <v>0.4073600481859411</v>
@@ -1053,7 +1053,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F13">
-        <v>0.02413727288602254</v>
+        <v>0.02413727288602276</v>
       </c>
       <c r="G13">
         <v>0.7402469135802467</v>
@@ -1083,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="P13">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>15</v>
@@ -1108,7 +1108,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F14">
-        <v>0.2745492459451345</v>
+        <v>0.2745492459451344</v>
       </c>
       <c r="G14">
         <v>0.7469444444444444</v>
@@ -1163,7 +1163,7 @@
         <v>0.2271062271062271</v>
       </c>
       <c r="F15">
-        <v>0.01091136045999133</v>
+        <v>0.01091136045999168</v>
       </c>
       <c r="G15">
         <v>0.3401000000000001</v>
@@ -1218,7 +1218,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F16">
-        <v>0.1455854394958989</v>
+        <v>0.1455854394958988</v>
       </c>
       <c r="G16">
         <v>0.9027777777777779</v>
@@ -1273,7 +1273,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F17">
-        <v>0.5186239472089468</v>
+        <v>0.5186239472089464</v>
       </c>
       <c r="G17">
         <v>0.4151929209183673</v>
@@ -1328,7 +1328,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F18">
-        <v>0.0498699736446202</v>
+        <v>0.04986997364462025</v>
       </c>
       <c r="G18">
         <v>0.9027777777777779</v>
@@ -1383,7 +1383,7 @@
         <v>0.2145328719723184</v>
       </c>
       <c r="F19">
-        <v>0.0444812322159495</v>
+        <v>0.04448123221594955</v>
       </c>
       <c r="G19">
         <v>0.6111111111111112</v>
@@ -1438,7 +1438,7 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="F20">
-        <v>0.05378569674578782</v>
+        <v>0.05378569674578824</v>
       </c>
       <c r="G20">
         <v>0.2622448979591837</v>
@@ -1493,7 +1493,7 @@
         <v>0.2897196261682243</v>
       </c>
       <c r="F21">
-        <v>0.1019516679235184</v>
+        <v>0.1019516679235185</v>
       </c>
       <c r="G21">
         <v>0.4822530864197531</v>
@@ -1548,7 +1548,7 @@
         <v>0.248</v>
       </c>
       <c r="F22">
-        <v>0.02689303999999549</v>
+        <v>0.02689303999999585</v>
       </c>
       <c r="G22">
         <v>0.3792</v>
@@ -1603,7 +1603,7 @@
         <v>0.1861861861861862</v>
       </c>
       <c r="F23">
-        <v>0.002771926326836644</v>
+        <v>0.002771926326836804</v>
       </c>
       <c r="G23">
         <v>0.9225</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="P23">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q23">
         <v>15</v>
@@ -1658,7 +1658,7 @@
         <v>0.2123287671232877</v>
       </c>
       <c r="F24">
-        <v>0.00315419079394494</v>
+        <v>0.003154190793945045</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>39</v>
       </c>
       <c r="P24">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.0146863087062081</v>
+        <v>0.01468630870620836</v>
       </c>
       <c r="G26">
         <v>0.686530612244898</v>
@@ -1817,7 +1817,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F27">
-        <v>0.01130002982502739</v>
+        <v>0.01130002982502742</v>
       </c>
       <c r="G27">
         <v>1.006944444444444</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="P27">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q27">
         <v>15</v>
@@ -1872,7 +1872,7 @@
         <v>0.1776504297994269</v>
       </c>
       <c r="F28">
-        <v>0.01130002982502737</v>
+        <v>0.01130002982502742</v>
       </c>
       <c r="G28">
         <v>1.006944444444444</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="P28">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q28">
         <v>15</v>
@@ -1927,7 +1927,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F29">
-        <v>0.0498699736446202</v>
+        <v>0.04986997364462024</v>
       </c>
       <c r="G29">
         <v>0.9027777777777779</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="P29">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q29">
         <v>15</v>
@@ -1982,7 +1982,7 @@
         <v>0.2627118644067797</v>
       </c>
       <c r="F30">
-        <v>0.2852074932652392</v>
+        <v>0.2852074932652394</v>
       </c>
       <c r="G30">
         <v>0.4175701530612245</v>
@@ -2037,7 +2037,7 @@
         <v>0.2322097378277154</v>
       </c>
       <c r="F31">
-        <v>0.1556265945531603</v>
+        <v>0.1556265945531602</v>
       </c>
       <c r="G31">
         <v>0.7608506944444444</v>
@@ -2092,7 +2092,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F32">
-        <v>0.1963072587097576</v>
+        <v>0.1963072587097577</v>
       </c>
       <c r="G32">
         <v>0.34765625</v>
@@ -2147,7 +2147,7 @@
         <v>0.2966507177033493</v>
       </c>
       <c r="F33">
-        <v>0.6068633760117337</v>
+        <v>0.6068633760117339</v>
       </c>
       <c r="G33">
         <v>0.2340364583333334</v>
@@ -2202,7 +2202,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="F34">
-        <v>0.5270445030072252</v>
+        <v>0.5270445030072249</v>
       </c>
       <c r="G34">
         <v>0.4721237244897959</v>
@@ -2312,7 +2312,7 @@
         <v>0.2767857142857143</v>
       </c>
       <c r="F36">
-        <v>0.05545829422091476</v>
+        <v>0.05545829422091497</v>
       </c>
       <c r="G36">
         <v>0.686530612244898</v>
@@ -2367,7 +2367,7 @@
         <v>0.1839762611275964</v>
       </c>
       <c r="F37">
-        <v>0.001236945685588575</v>
+        <v>0.001236945685588669</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2422,7 +2422,7 @@
         <v>0.2910798122065728</v>
       </c>
       <c r="F38">
-        <v>0.06812048270106578</v>
+        <v>0.0681204827010662</v>
       </c>
       <c r="G38">
         <v>0.4414448979591837</v>
@@ -2477,7 +2477,7 @@
         <v>0.2431372549019608</v>
       </c>
       <c r="F39">
-        <v>0.01089577315301338</v>
+        <v>0.01089577315301348</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2581,7 +2581,7 @@
         <v>0.2393822393822394</v>
       </c>
       <c r="F41">
-        <v>0.4382144437328441</v>
+        <v>0.4382144437328442</v>
       </c>
       <c r="G41">
         <v>0.5292881944444444</v>
@@ -2636,7 +2636,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F42">
-        <v>0.02413727288602258</v>
+        <v>0.02413727288602275</v>
       </c>
       <c r="G42">
         <v>0.7402469135802467</v>
@@ -2666,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="P42">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q42">
         <v>15</v>
@@ -2691,7 +2691,7 @@
         <v>0.2672413793103448</v>
       </c>
       <c r="F43">
-        <v>0.04165861565408996</v>
+        <v>0.04165861565409008</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2740,7 +2740,7 @@
         <v>0.256198347107438</v>
       </c>
       <c r="F44">
-        <v>0.01871153087579441</v>
+        <v>0.01871153087579478</v>
       </c>
       <c r="G44">
         <v>0.2601133786848072</v>
@@ -2795,7 +2795,7 @@
         <v>0.2046204620462046</v>
       </c>
       <c r="F45">
-        <v>0.003790535553194765</v>
+        <v>0.00379053555319485</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>0.2375478927203065</v>
       </c>
       <c r="F46">
-        <v>0.2279984327127862</v>
+        <v>0.227998432712786</v>
       </c>
       <c r="G46">
         <v>0.70703125</v>
@@ -2899,7 +2899,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F47">
-        <v>0.005298875417603563</v>
+        <v>0.005298875417603813</v>
       </c>
       <c r="G47">
         <v>0.6949483497102544</v>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
       <c r="P47">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q47">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>0.2066666666666667</v>
       </c>
       <c r="F48">
-        <v>0.005298875417603584</v>
+        <v>0.005298875417603784</v>
       </c>
       <c r="G48">
         <v>0.6949483497102544</v>
@@ -2984,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="P48">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q48">
         <v>14</v>
@@ -3009,7 +3009,7 @@
         <v>0.161038961038961</v>
       </c>
       <c r="F49">
-        <v>0.006905590848685265</v>
+        <v>0.006905590848685302</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3058,7 +3058,7 @@
         <v>0.191358024691358</v>
       </c>
       <c r="F50">
-        <v>0.03408863327290827</v>
+        <v>0.03408863327290832</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -3113,7 +3113,7 @@
         <v>0.1722222222222222</v>
       </c>
       <c r="F51">
-        <v>0.002146866100449228</v>
+        <v>0.002146866100449363</v>
       </c>
       <c r="G51">
         <v>0.8888888888888888</v>
@@ -3168,7 +3168,7 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="F52">
-        <v>0.08230408821726883</v>
+        <v>0.08230408821726885</v>
       </c>
       <c r="G52">
         <v>0.78125</v>
@@ -3223,7 +3223,7 @@
         <v>0.1557788944723618</v>
       </c>
       <c r="F53">
-        <v>0.0002505773915409316</v>
+        <v>0.0002505773915409819</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3272,7 +3272,7 @@
         <v>0.2818181818181818</v>
       </c>
       <c r="F54">
-        <v>0.1210769133230428</v>
+        <v>0.1210769133230429</v>
       </c>
       <c r="G54">
         <v>0.36328125</v>
@@ -3327,7 +3327,7 @@
         <v>0.1993569131832797</v>
       </c>
       <c r="F55">
-        <v>0.005447925395850025</v>
+        <v>0.005447925395850112</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3376,7 +3376,7 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="F56">
-        <v>0.5730798804738928</v>
+        <v>0.5730798804738931</v>
       </c>
       <c r="G56">
         <v>0.2646517148526077</v>
@@ -3431,7 +3431,7 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="F57">
-        <v>0.1455854394958988</v>
+        <v>0.1455854394958987</v>
       </c>
       <c r="G57">
         <v>0.9027777777777779</v>
@@ -3486,7 +3486,7 @@
         <v>0.2339622641509434</v>
       </c>
       <c r="F58">
-        <v>0.1613689194542328</v>
+        <v>0.1613689194542332</v>
       </c>
       <c r="G58">
         <v>0.5017361111111112</v>
@@ -3596,7 +3596,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F60">
-        <v>0.04986997364462016</v>
+        <v>0.04986997364462023</v>
       </c>
       <c r="G60">
         <v>0.9027777777777779</v>
@@ -3651,7 +3651,7 @@
         <v>0.1931464174454829</v>
       </c>
       <c r="F61">
-        <v>0.04986997364462019</v>
+        <v>0.04986997364462024</v>
       </c>
       <c r="G61">
         <v>0.9027777777777779</v>
@@ -3706,7 +3706,7 @@
         <v>0.2206405693950178</v>
       </c>
       <c r="F62">
-        <v>0.0245274610435953</v>
+        <v>0.02452746104359534</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3755,7 +3755,7 @@
         <v>0.2384615384615385</v>
       </c>
       <c r="F63">
-        <v>0.3552799123856286</v>
+        <v>0.3552799123856282</v>
       </c>
       <c r="G63">
         <v>0.6091666666666665</v>
@@ -3810,7 +3810,7 @@
         <v>0.2938388625592417</v>
       </c>
       <c r="F64">
-        <v>0.7252640270422739</v>
+        <v>0.725264027042274</v>
       </c>
       <c r="G64">
         <v>0.2385430839002267</v>
